--- a/Result/checksun_type/休閒車業.xlsx
+++ b/Result/checksun_type/休閒車業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>95.78</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>96.92</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>99.07</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>99.06999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>395003527.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>181919288.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>181919288.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>187058193.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>193927499.22</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>193927499.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>6419019.784328848</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>395003527</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>395003527.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>93.52000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>96.97</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>96.97</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>99.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>54544500.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>126353866.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>126353866.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>163323490.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>188834483.02</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>188834483.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-13722667.17985916</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>54544500</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>54544500.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>92.8</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>97.46</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>99.19</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>97.45999999999999</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>99.19</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>167042468.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>157377357.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>157377357.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>175719604.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>189229347.44</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>189229347.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-5528657.550847054</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>167042468</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>167042468.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>92.68</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>98.04</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>99.35</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>99.34999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>172883735.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>168817760.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>168817760.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>203177017.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>187689182.78</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>187689182.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-5678831.168299526</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>172883735</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>172883735.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>93.08000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>98.76</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>99.57</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>99.56999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>120122212.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>191928187.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>191928187.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>198027394.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>186018832.2</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>186018832.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-6316399.544363767</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>120122212</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>120122212.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>93.8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>99.79</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>99.79000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>117176418.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>192197098.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>192197098</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>197197123.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>184280310.86</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>184280310.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1348605.490728259</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>117176418</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>117176418.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>94.44</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>100.02</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>100.03</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>100.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>209661956.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>200293113.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>200293113.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>203683175.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>182928351.54</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>182928351.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>6112028.424848467</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>209661956</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>209661956.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>95.08</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>100.66</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>100.23</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>100.66</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>100.23</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>224244481.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>194061851.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>194061851.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>201690387.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>181709024.64</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>181709024.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>6642625.360499233</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>224244481</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>224244481.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>95.24</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>101.09</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>100.41</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>101.09</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>100.41</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>288435872.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>237536273.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>237536273.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>189566439.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>178899166.4</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>178899166.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>5600970.969982475</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>288435872</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>288435872.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>95.53999999999999</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>101.44</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>100.54</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>100.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>121466763.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>204126602.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>204126602</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>177082901.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>174013258.16</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>174013258.16</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2964790.443969399</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>121466763</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>121466763.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>96.47999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>101.64</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>100.72</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>100.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>157656495.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>202197149.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>202197149.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>174094628.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>172663321.18</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>172663321.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>2793840.301955402</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>157656495</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>157656495.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>90.96000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>94.86</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>101.33</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>101.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>183901765.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>137151954.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>137151954.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>161211464.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>151502855.16</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>151502855.16</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3500747.056107074</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>183901765</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>183901765.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>89.5</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>95.23</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>101.63</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>101.63</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>59255609.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>119066850.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>119066850.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>148168771.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>151985498.76</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>151985498.76</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-7603311.738091618</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>59255609</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>59255609.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>89.10000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>95.94</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>101.97</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>101.97</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>125954486.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>181566538.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>181566538.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>158843029.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>152811136.6</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>152811136.6</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>162373.7068622708</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>125954486</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>125954486.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>89.92</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>96.72</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>102.34</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>102.34</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>154594030.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>174547007.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>174547007.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>201318561.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>157792820.98</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>157792820.98</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>4104102.745837003</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>154594030</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>154594030.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>90.86</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>97.62</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>102.72</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>102.72</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>162053883.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>192196683.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>192196683.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>194430749.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>160301624.3</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>160301624.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>6520046.560592502</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>162053883</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>162053883.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>92.22</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>98.36</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>103.19</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>103.19</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>93476245.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>185270975.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>185270975.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>192566243.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>161612670.04</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>161612670.04</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>8939266.097364902</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>93476245</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>93476245.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>93.34</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>99.03</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>103.76</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>103.76</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>371754047.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>177270692.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>177270692.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>192111461.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>165042383.86</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>165042383.86</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>19423638.57499102</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>371754047</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>371754047.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>94.34</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>99.76</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>104.36</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>104.36</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>90856834.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>136119520.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>136119520</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>176019001.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>163699705.2</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>163699705.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>3892133.379635811</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>90856834</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>90856834.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>94.54</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>100.21</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>104.83</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>104.83</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>242842407.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>228090115.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>228090115.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>174982972.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>166875363.94</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>166875363.94</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>11661394.01556993</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>242842407</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>242842407.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>95.26</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>105.26</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>105.26</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>127425343.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>196664816.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>196664816.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>160026284.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>166513716.06</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>166513716.06</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>6059690.887776881</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>127425343</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>127425343.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>96.28</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>100.83</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>105.68</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>105.68</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>53474832.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>199861510.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>199861510.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>152288075.7</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>170802756.36</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>170802756.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>10206954.31636623</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>53474832</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>53474832.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>152.3</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>153.4</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>159.84</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>159.84</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>24220.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>23514.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>23514.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>30705.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>69349.94</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>69349.94</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-5678.921837583708</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>24220</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>24220.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>151.2</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>153.35</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>159.79</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>153.35</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>159.79</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>23049.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>22212.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>22212.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>43769.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>70201.64</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>70201.64</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-5958.240678264159</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>23049</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>23049.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>150.2</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>153.45</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>159.79</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>153.45</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>159.79</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>21478.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>22226.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>22226.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>44192.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>72842.34</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>72842.34</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-6019.008997869663</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>21478</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>21478.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>151.0</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>160.04</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>154</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>160.04</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>29662.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>19530.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>19530.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>46504.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>77624.82</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>77624.82000000001</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-5722.534847382187</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>29662</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>29662.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>152.3</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>154.52</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>160.45</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>154.52</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>160.45</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>19164.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>16364.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>16364.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>46649.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>82460.06</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>82460.06</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-5971.481244993556</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>19164</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>19164.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>154.2</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>154.65</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>160.68</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>154.65</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>160.68</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>17711.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>37897.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>37897.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>52355.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>85795.38</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>85795.38</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-4989.066054260038</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>17711</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>17711.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>154.6</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>154.85</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>160.84</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>154.85</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>160.84</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>23118.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>65325.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>65325.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>55923.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>86515.58</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>86515.58</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-3251.756279845715</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>23118</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>23118.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>154.7</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>155.18</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>160.99</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>155.18</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>160.99</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>7999.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>66157.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>66157.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>55859.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>88955.2</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>88955.2</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1233.072449259351</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>7999</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>7999.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>154.0</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>155.43</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>160.8</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>160.8</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>13830.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>73478.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>73478</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>56584.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>89866.12</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>89866.12</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>3314.692753337571</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>13830</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>13830.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>153.6</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>155.85</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>160.7</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>155.85</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>160.7</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>126828.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>76935.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>76935.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>57232.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>91374.88</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>91374.88</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>9068.368301571129</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>126828</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>126828.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>152.8</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>156.05</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>160.51</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>156.05</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>160.51</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>154852.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>66813.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>66813.39999999999</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>49612.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>89832.76</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>89832.75999999999</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>4857.105931134378</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>154852</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>154852.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>5.802</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>6.05</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>792.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1074.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1074.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1213.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>916.84</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>916.84</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>16.17733360399779</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>792</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>792.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>5.786</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>6.05</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1000.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1235.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1235.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1283.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>924.2</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>924.2</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>55.5198577868448</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1000</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>5.796</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>6.06</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1313.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1531.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1531.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1353.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>920.6</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>920.6</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>87.45489741281062</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1313</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1313.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>5.85</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>5.99</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>6.07</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1682.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1323.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1323.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1312.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>917.88</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>917.88</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>96.41727911373277</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1682</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1682.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>5.904</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>6.01</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>6.08</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>6.08</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>584.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1191.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1191</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1208.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>904.94</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>904.9400000000001</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>66.24149300384556</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>584</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>584.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>5.936</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>6.09</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1598.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1352.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1352</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1203.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>902.92</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>902.92</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>138.4103166681552</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1598</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1598.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>5.988</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>6.1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>2481.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1332.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1332.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1088.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>880.4</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>880.4</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>127.9225534504494</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2481</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2481.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>5.998</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>6.11</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>6.11</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>272.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1175.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1175.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>943.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>839.68</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>839.6799999999999</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>13.76422908763914</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>272</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>272.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>6.006</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>6.12</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>6.12</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1020.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1302.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1302</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1026.4</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>849.54</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>849.54</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>86.86790038763729</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1020</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>6.014</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>6.13</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>6.13</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1389.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1226.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1226</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1003.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>844.24</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>844.24</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>108.0564343737905</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1389</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1389.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>6.039999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>6.14</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>6.14</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1500.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1055.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1055.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>944.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>837.58</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>837.58</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>94.93089598351673</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1500</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>40.69</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>41.2</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>42.39</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>42.39</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>801944.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>779314.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>779314</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>923865.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>767710.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>767710</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-38479.10849819274</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>801944</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>801944.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>40.62</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>41.25</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>42.45</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>42.45</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>653914.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>822249.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>822249.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>949377.6</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>757849.12</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>757849.12</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-37514.9607102602</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>653914</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>653914.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>40.67</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>42.5</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>740294.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>921170.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>921170</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>992266.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>755626.24</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>755626.24</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-18937.42955927562</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>740294</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>740294.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>40.76</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>42.56</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>42.56</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>662798.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1080342.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1080342.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1059655.6</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>744336.7</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>744336.7</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-976.7625736093614</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>662798</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>662798.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>40.91</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>42.64</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>42.64</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1037620.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1105853.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1105853.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1059696.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>734586.74</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>734586.74</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>33019.36035497149</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1037620</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1037620.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>41.07</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>42.7</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1016623.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1068417.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1068417.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1067696.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>716447.34</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>716447.34</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>40246.48738312372</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1016623</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1016623.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>41.28</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>41.7</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>42.76</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>42.76</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1148515.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1076505.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1076505.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1029919.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>706711.88</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>706711.88</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>51383.25858822942</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1148515</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1148515.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>41.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>41.78</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>42.83</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>1536158.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1063362.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1063362.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1002812.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>689075.58</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>689075.58</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>51326.5296459439</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1536158</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1536158.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>41.5</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>41.87</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>42.88</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>42.88</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>790350.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1038968.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1038968.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>919814.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>660963.3</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>660963.3</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>7879.219383895048</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>790350</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>790350.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>41.55</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>41.93</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>42.92</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>42.92</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>850440.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>1013540.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>1013540.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>909999.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>649506.3</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>649506.3</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>25438.23260297196</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>850440</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>850440.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>41.51000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>42.01</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>42.97</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>42.97</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>1057064.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1066974.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1066974.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>946440.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>656444.38</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>656444.38</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>43175.8146086901</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>1057064</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>1057064.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>18.37</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>236.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>156.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>156.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>264.9</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>305.26</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>305.26</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-49.7741195492373</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>236</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>236.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>18.3</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>19.7</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>182.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>182</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>311.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>310.96</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>310.96</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-57.40321068268287</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>23</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>18.3</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>19.75</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>219.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>219.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>369.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>321.36</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>321.36</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-43.43036906322362</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>18.3</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>19.79</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>220.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>257.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>257.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>465.6</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>324.52</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>324.52</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-19.56093928316665</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>220</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>18.39</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>19.84</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>19.84</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>303.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>362.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>362.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>483.8</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>322.6</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>322.6</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-8.227434622972225</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>303</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>303.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>18.53</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>19.21</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>19.9</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>363.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>373.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>373.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>474.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>318.66</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>318.66</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-0.6357338718740948</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>363</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>363.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>18.56</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>211.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>441.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>441.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>460.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>311.98</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>311.98</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>3.803686267975877</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>211</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>211.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>18.61</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>19.38</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>19.99</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>518.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>518.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>464.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>309.96</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>309.96</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>26.29558338676253</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>189</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>18.67</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>20.03</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>20.03</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>745.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>674.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>674</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>480.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>309.96</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>309.96</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>59.84487986407328</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>745</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>745.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>18.73</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>19.52</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>20.06</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>20.06</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>358.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>605.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>605.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>438.1</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>298.12</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>298.12</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>46.06370055080038</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>358</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>358.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>18.89</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>20.1</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>704.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>576.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>576.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>431.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>300.5</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>300.5</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>66.19545508359613</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>704</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>90.05999999999999</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>89.31</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>89.36</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>89.31</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>89.36</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>19372606.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>8117469.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>8117469.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>12272410.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>15664883.56</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>15664883.56</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-800032.045709094</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>19372606</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>19372606.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>89.28</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>89.24</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>89.23999999999999</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>4222845.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>5963450.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>5963450.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>11511634.8</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>16801150.48</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>16801150.48</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-1838990.833036141</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>4222845</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>4222845.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>88.96000000000001</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>89.22</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>89.25</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>89.22</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>89.25</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>2493176.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>8201980.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>8201980.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>13476741.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>17300052.22</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>17300052.22</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-1634350.749466345</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>2493176</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>2493176.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>89.1</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>89.32</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>89.28</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>89.28</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>7687302.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>9391342.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>9391342.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>14737345.1</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>17862449.48</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>17862449.48</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-1098316.424742838</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>7687302</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>7687302.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>89.56</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>89.48</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>89.37</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>89.37</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>6811419.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>11306400.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>11306400.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>14638335.9</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>17856750.8</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>17856750.8</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-849841.0171113014</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>6811419</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>6811419.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>90.3</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>89.59</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>89.46</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>89.45999999999999</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>8602510.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>16427351.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>16427351.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>14254243.2</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>17787154.04</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>17787154.04</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-370680.0770265609</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>8602510</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>8602510.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>90.2</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>89.73</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>89.56</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>89.56</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>15415494.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>17059819.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>17059819.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>14586125.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>17703060.88</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>17703060.88</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>135171.5187025927</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>15415494</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>15415494.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>89.6</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>89.88</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>89.88</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>89.63</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>8439987.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>18751502.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>18751502.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>13955499.5</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>17495092.1</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>17495092.1</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>123026.5297905747</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>8439987</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>8439987.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>88.8</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>89.96</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>89.68</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>89.95999999999999</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>89.68000000000001</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>17262591.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>20083347.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>20083347.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>13612717.1</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>17538781.28</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>17538781.28</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>848658.4909951724</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>17262591</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>17262591.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>88.14</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>89.71</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>89.70999999999999</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>32416176.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>17970271.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>17970271.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>12704993.1</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>17355408.12</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>17355408.12</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>909687.3466090541</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>32416176</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>32416176.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>87.36</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>89.73</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>89.73</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>11764848.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>12081134.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>12081134.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>10251199.2</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>16866047.64</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>16866047.64</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-659215.8006071486</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>11764848</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>11764848.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>165.7</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>174.2</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>183.11</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>183.11</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>51512347.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>40425814.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>40425814</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>40920917.2</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>52312376.98</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>52312376.98</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-2256895.638391986</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>51512347</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>51512347.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>164.7</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>175.18</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>183.38</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>175.18</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>183.38</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>33708865.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>33703844.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>33703844</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>40141577.5</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>53784844.84</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>53784844.84</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-3404395.624385178</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>33708865</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>33708865.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>164.6</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>176.32</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>183.83</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>176.32</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>183.83</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>35107605.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>40048859.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>40048859</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>58838169.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>54164381.18</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>54164381.18</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-3014579.832075976</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>35107605</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>35107605.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>165.0</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>177.48</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>184.27</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>177.48</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>184.27</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>40530740.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>39100979.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>39100979</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>59050866.9</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>54248969.5</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>54248969.5</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-2499901.563345835</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>40530740</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>40530740.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>166.1</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>178.82</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>184.8</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>178.82</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>184.8</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>41269513.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>39062362.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>39062362</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>57015102.4</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>54573696.46</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>54573696.46</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-2256414.87361186</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>41269513</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>41269513.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>167.3</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>180.05</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>185.27</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>180.05</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>185.27</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>17902497.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>41416020.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>41416020.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>54910955.1</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>55839343.5</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>55839343.5</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-1907144.749934323</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>17902497</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>17902497.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>168.9</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>181.15</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>185.85</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>181.15</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>185.85</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>65433940.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>46579311.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>46579311</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>64085852.4</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>57880563.72</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>57880563.72</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>1163533.739245526</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>65433940</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>65433940.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>170.2</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>182.2</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>186.3</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>186.3</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>30368205.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>77627480.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>77627480.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>61071190.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>56998098.52</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>56998098.52</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>416007.9116722494</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>30368205</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>30368205.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>173.0</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>183.1</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>186.68</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>186.68</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>40337655.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>79000754.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>79000754.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>62142524.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>56848150.98</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>56848150.98</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>3090299.482579283</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>40337655</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>40337655.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>176.1</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>183.98</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>187.04</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>183.98</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>187.04</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>53037805.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>74967842.8</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>74967842.8</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>62562364.9</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>56967307.56</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>56967307.56</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>5732192.816640072</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>53037805</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>53037805.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>178.7</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>184.7</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>187.41</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>187.41</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>43718950.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>68405889.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>68405889.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>59810718.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>57136125.82</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>57136125.82</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>7940874.621846907</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>43718950</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>43718950.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>1578.0</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>1508.25</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>1297.34</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>1508.25</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>1297.34</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>8660559640.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>12655765945.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>12655765945.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>9186859988.8</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>4926093528.12</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>4926093528.12</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>1587065451.454584</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>8660559640</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>8660559640.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>1594.0</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>1506.25</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>1289.84</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>1506.25</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>1289.84</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>14268998085.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>11903064950.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>11903064950.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>8830581319.3</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>4817341249.12</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>4817341249.12</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>2015843897.12149</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>14268998085</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>14268998085.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>1599.0</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>1501.25</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>1281.64</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>1501.25</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1281.64</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>28742044615.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>10298542898.2</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>10298542898.2</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>8042654289.3</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>4598697520.32</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>4598697520.32</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>1955485989.784161</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>28742044615</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>28742044615.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>1612.0</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>1491.75</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>1272.24</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1272.24</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>6169714440.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>5728226103.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>5728226103</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>5811772650.8</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>4091228347.42</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>4091228347.42</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>248738065.7385426</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>6169714440</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>6169714440.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>1478.0</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>1261.84</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>1478</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1261.84</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>5437512946.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>5661854900.6</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>5661854900.6</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>5608775910.3</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>4014085333.32</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>4014085333.32</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>220107190.6469994</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>5437512946</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>5437512946.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>1580.0</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>1460.0</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>1249.74</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>1249.74</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>4897054665.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>5717954032.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>5717954032.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>5414291186.7</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>4036813613.2</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>4036813613.2</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>249795129.4931173</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>4897054665</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>4897054665.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>1564.0</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>1445.5</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>1239.34</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>1445.5</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1239.34</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>6246387825.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>5758097688.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>5758097688.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>5400232874.2</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>4111558830.4</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>4111558830.4</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>341191460.4699583</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>6246387825</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>6246387825.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>1560.0</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>1431.5</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>1227.28</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>1431.5</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>1227.28</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>5890460639.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>5786765680.4</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>5786765680.4</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>5177128699.2</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>4046244405.4</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>4046244405.4</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>315000828.2772322</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>5890460639</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>5890460639.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>1542.0</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>1415.0</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>1213.96</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>1415</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>1213.96</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>5837858428.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>5895319198.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>5895319198.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>5008164336.8</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>4019510992.36</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>4019510992.36</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>304470665.4920092</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>5837858428</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>5837858428.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>1521.0</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>1203.08</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1203.08</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>5718008605.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>5555696920.0</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>5555696920</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>4684194498.0</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>4026606885.46</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>4026606885.46</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>284189574.6384048</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>5718008605</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>5718008605.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>1474.0</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>1379.0</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>1192.48</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>1379</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>1192.48</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>5097772945.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>5110628341.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>5110628341</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>4542311051.0</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>4058950208.26</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>4058950208.26</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>257908012.5033131</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>5097772945</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>5097772945.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>54.96</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>57.98</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>55.25</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>55.25</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>94586.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>107718.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>107718.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>208884.6</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>314451.14</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>314451.14</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-111682.6264215373</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>94586</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>94586.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>54.3</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>57.89</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>55.26</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>55.26</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>129103.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>114178.6</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>114178.6</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>273700.9</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>316821.38</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>316821.38</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-111254.8685193221</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>129103</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>129103.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>53.7</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>57.77</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>55.32</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>55.32</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>105747.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>122177.6</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>122177.6</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>370839.1</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>319692.18</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>319692.18</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-110368.6476404673</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>105747</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>105747.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>53.84</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>57.72</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>55.47</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>55.47</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>89972.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>132582.0</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>132582</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>609994.5</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>321358.8</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>321358.8</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-102658.4518263723</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>89972</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>89972.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>54.28000000000001</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>57.67</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>55.61</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>55.61</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>119185.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>170198.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>170198.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>798986.8</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>322062.64</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>322062.64</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-86287.33452672337</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>119185</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>119185.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>54.86</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>57.57</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>55.72</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>55.72</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>126886.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>310050.6</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>310050.6</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>891290.4</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>323151.9</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>323151.9</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-62948.29786555609</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>126886</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>126886.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>56.98</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>57.68</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>55.88</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>55.88</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>169098.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>433223.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>433223.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>1110135.8</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>326491.78</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>326491.78</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-28183.77056869026</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>169098</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>169098.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>59.61999999999999</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>56.1</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>56.1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>157769.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>619500.6</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>619500.6</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>1108537.2</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>328362.14</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>328362.14</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>17963.6888042856</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>157769</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>157769.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>61.88</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>57.83</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>56.26</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>278055.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>1087407.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>1087407</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>1103202.5</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>331825.14</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>331825.14</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>84460.89187981223</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>278055</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>278055.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>64.4</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>56.45</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>56.45</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>818445.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>1427775.0</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>1427775</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>1083544.2</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>335315.52</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>335315.52</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>163552.6501348572</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>818445</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>818445.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>65.38</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>57.39</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>56.65</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>56.65</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>742749.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>1472530.2</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>1472530.2</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>1018546.8</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>336321.52</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>336321.52</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>212800.7815658193</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>742749</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>742749.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>10702402903</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>9579043601</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>16911194399</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>15812987742</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>15882778006</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>10973548400</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>12353712685</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>10709769939</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>18182742782</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>10733728288</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>13958553198</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>26.97</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>28.44</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>1044.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>604.8</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>604.8</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>653.6</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>721.72</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>721.72</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>18.76122793216973</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>1044</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>1044.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>26.91</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>27.48</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>28.5</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>303.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>604.0</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>604</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>644.2</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>727.34</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>727.34</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-21.73475679592491</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>303</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>303.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>26.93</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>27.57</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>28.57</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>28.57</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>536.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>686.8</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>686.8</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>636.8</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>728.02</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>728.02</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>0.5829349066515306</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>536</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>536.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>27.68</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>28.65</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>406.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>669.2</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>669.2</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>616.6</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>727.6</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>727.6</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>7.480246806523041</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>406</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>406.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>27.12</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>27.77</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>28.72</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>735.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>697.0</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>697</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>592.3</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>729.82</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>729.8200000000001</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>30.99496927753512</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>735</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>735.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>27.08</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>27.86</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>28.8</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>1040.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>702.4</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>702.4</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>548.5</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>722.34</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>722.34</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>28.23046676192621</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>1040</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>1040.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>27.17</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>28.9</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>717.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>684.4</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>684.4</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>461.9</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>716.18</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>716.1799999999999</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>-9.405624930441036</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>717</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>717.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>27.22</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>28.12</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>29</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>448.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>586.8</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>586.8</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>418.5</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>709.34</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>709.34</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>-28.22841217202119</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>448</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>27.23</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>28.14</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>29.11</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>29.11</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>545.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>564.0</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>564</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>427.7</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>760.92</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>760.92</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>-25.28852208242074</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>545</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>545.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>27.27999999999999</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>28.19</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>29.2</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>762.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>487.6</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>487.6</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>424.6</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>751.52</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>751.52</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-30.57837473719076</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>762</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>762.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>27.4</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>28.26</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>29.3</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>950.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>394.6</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>394.6</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>396.6</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>799.74</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>799.74</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-60.29322228910547</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>950</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>950.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
